--- a/gal/Assets/Resources/VNovelizerRes/ExcelVNScripts/第八章1.xlsx
+++ b/gal/Assets/Resources/VNovelizerRes/ExcelVNScripts/第八章1.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="12080"/>
+    <workbookView windowWidth="24750" windowHeight="12790"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="78">
   <si>
     <t>ID</t>
   </si>
@@ -273,14 +273,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -748,148 +741,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -898,9 +891,9 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2332,7 +2325,9 @@
       <c r="A51" s="2">
         <v>1049</v>
       </c>
-      <c r="B51" s="3"/>
+      <c r="B51" s="3" t="s">
+        <v>13</v>
+      </c>
       <c r="C51" s="2"/>
       <c r="D51" s="2"/>
       <c r="E51" s="2"/>
